--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F9A0F87-26E0-4201-8544-5942F4FDC33A}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6D3AACD-61D5-4E20-9BC2-4A4EF64A7A83}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
+    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
   <sheets>
-    <sheet name="FactTable" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="FactTable" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="51">
   <si>
     <t>Maplewood HS</t>
   </si>
@@ -142,6 +149,54 @@
   <si>
     <t>PlayerID</t>
   </si>
+  <si>
+    <t>F_PlayerName</t>
+  </si>
+  <si>
+    <t>Olivia Hart</t>
+  </si>
+  <si>
+    <t>Mia Russo</t>
+  </si>
+  <si>
+    <t>Emma Torres</t>
+  </si>
+  <si>
+    <t>Sophie Kim</t>
+  </si>
+  <si>
+    <t>Ava Nguyen</t>
+  </si>
+  <si>
+    <t>Chloe Banks</t>
+  </si>
+  <si>
+    <t>Riley Patel</t>
+  </si>
+  <si>
+    <t>Jenna Walsh</t>
+  </si>
+  <si>
+    <t>Natalie Cruz</t>
+  </si>
+  <si>
+    <t>Lauren Scott</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Count of PenType</t>
+  </si>
 </sst>
 </file>
 
@@ -213,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -224,6 +279,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -239,6 +299,1716 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="DimPlayers"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>Olivia Hart</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>Mia Russo</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>Emma Torres</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>Sophie Kim</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Ava Nguyen</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>Chloe Banks</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Riley Patel</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Jenna Walsh</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Natalie Cruz</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Lauren Scott</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Chris Napoli" refreshedDate="46083.53809814815" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="70" xr:uid="{9B219841-7E8E-46DC-9F7F-1EF254B500FA}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:R71" sheet="FactTable"/>
+  </cacheSource>
+  <cacheFields count="18">
+    <cacheField name="PlayerID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
+    </cacheField>
+    <cacheField name="F_PlayerName" numFmtId="0">
+      <sharedItems count="10">
+        <s v="Olivia Hart"/>
+        <s v="Mia Russo"/>
+        <s v="Emma Torres"/>
+        <s v="Sophie Kim"/>
+        <s v="Ava Nguyen"/>
+        <s v="Chloe Banks"/>
+        <s v="Riley Patel"/>
+        <s v="Jenna Walsh"/>
+        <s v="Natalie Cruz"/>
+        <s v="Lauren Scott"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Date" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="OpponentName" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Goals" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
+    </cacheField>
+    <cacheField name="Assists" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
+    </cacheField>
+    <cacheField name="Shots" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="7"/>
+    </cacheField>
+    <cacheField name="GBs" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="5"/>
+    </cacheField>
+    <cacheField name="TOs" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
+    </cacheField>
+    <cacheField name="DrawAtts" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="4"/>
+    </cacheField>
+    <cacheField name="DrawControls" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
+    </cacheField>
+    <cacheField name="ShotsFaced" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="11"/>
+    </cacheField>
+    <cacheField name="Saves" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="8"/>
+    </cacheField>
+    <cacheField name="WomanUpGoals" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="WomanDownGoals" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="CTOs" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
+    </cacheField>
+    <cacheField name="PenType" numFmtId="0">
+      <sharedItems containsBlank="1" count="5">
+        <m/>
+        <s v="Green"/>
+        <s v="Yellow"/>
+        <s v="12m"/>
+        <s v="Red"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="MinsServed" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="70">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="9"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="11"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <x v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F71C58A-B4F5-465D-857D-A0DA0D629E32}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="16"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of PenType" fld="16" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -557,100 +2327,318 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FECCF03-21CB-4BCE-B5AE-16126AAD8F80}">
+  <dimension ref="A3:G15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6">
+        <v>2</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="6">
+        <v>3</v>
+      </c>
+      <c r="C15" s="6">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6">
+        <v>4</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{675130FE-5529-48C3-883E-D019D34D4137}">
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
+        <f>_xlfn.XLOOKUP(B2,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
       <c r="E2" s="2">
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
@@ -673,33 +2661,37 @@
       <c r="O2" s="2">
         <v>0</v>
       </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
+        <f>_xlfn.XLOOKUP(B3,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
       <c r="E3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
@@ -724,45 +2716,49 @@
       <c r="O3" s="1">
         <v>0</v>
       </c>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
+        <f>_xlfn.XLOOKUP(B4,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
       <c r="E4" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>2</v>
       </c>
       <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
         <v>4</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>3</v>
       </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
       <c r="L4" s="2">
         <v>0</v>
       </c>
@@ -775,29 +2771,33 @@
       <c r="O4" s="2">
         <v>0</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
+        <f>_xlfn.XLOOKUP(B5,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
         <v>2</v>
@@ -806,13 +2806,13 @@
         <v>2</v>
       </c>
       <c r="I5" s="1">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1">
         <v>3</v>
       </c>
-      <c r="J5" s="1">
-        <v>2</v>
-      </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -826,44 +2826,48 @@
       <c r="O5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
+        <f>_xlfn.XLOOKUP(B6,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
       <c r="E6" s="2">
         <v>0</v>
       </c>
       <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
         <v>3</v>
       </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
         <v>2</v>
       </c>
       <c r="K6" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -875,40 +2879,44 @@
         <v>0</v>
       </c>
       <c r="O6" s="2">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
+        <f>_xlfn.XLOOKUP(B7,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
       <c r="E7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -923,34 +2931,38 @@
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
         <v>1</v>
       </c>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
+        <f>_xlfn.XLOOKUP(B8,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -959,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
@@ -977,28 +2989,32 @@
         <v>0</v>
       </c>
       <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
         <v>3</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
+        <f>_xlfn.XLOOKUP(B9,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
@@ -1006,13 +3022,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
         <v>3</v>
       </c>
-      <c r="H9" s="1">
-        <v>2</v>
-      </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -1030,26 +3046,30 @@
         <v>0</v>
       </c>
       <c r="O9" s="1">
-        <v>2</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
+        <f>_xlfn.XLOOKUP(B10,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
       <c r="E10" s="2">
         <v>0</v>
       </c>
@@ -1057,14 +3077,14 @@
         <v>0</v>
       </c>
       <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
         <v>4</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>3</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
       <c r="J10" s="2">
         <v>0</v>
       </c>
@@ -1078,29 +3098,33 @@
         <v>0</v>
       </c>
       <c r="N10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="2">
         <v>1</v>
       </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P10" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
+        <f>_xlfn.XLOOKUP(B11,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
@@ -1120,11 +3144,11 @@
         <v>0</v>
       </c>
       <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
         <v>5</v>
       </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
       <c r="M11" s="1">
         <v>0</v>
       </c>
@@ -1134,35 +3158,39 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
+        <f>_xlfn.XLOOKUP(B12,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="2">
-        <v>2</v>
-      </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
         <v>3</v>
       </c>
-      <c r="G12" s="2">
-        <v>2</v>
-      </c>
       <c r="H12" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
@@ -1177,46 +3205,50 @@
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2">
-        <v>1</v>
-      </c>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
+        <f>_xlfn.XLOOKUP(B13,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
@@ -1234,47 +3266,51 @@
         <v>0</v>
       </c>
       <c r="O13" s="1">
-        <v>1</v>
-      </c>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
+        <f>_xlfn.XLOOKUP(B14,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="2">
-        <v>2</v>
-      </c>
       <c r="E14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
         <v>4</v>
       </c>
-      <c r="G14" s="2">
-        <v>2</v>
-      </c>
       <c r="H14" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
         <v>4</v>
       </c>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <v>3</v>
       </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
       <c r="L14" s="2">
         <v>0</v>
       </c>
@@ -1287,38 +3323,42 @@
       <c r="O14" s="2">
         <v>0</v>
       </c>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
+        <f>_xlfn.XLOOKUP(B15,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
       <c r="E15" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
         <v>4</v>
       </c>
-      <c r="H15" s="1">
-        <v>2</v>
-      </c>
       <c r="I15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
@@ -1336,77 +3376,85 @@
         <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>1</v>
-      </c>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
+        <f>_xlfn.XLOOKUP(B16,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
       <c r="E16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
         <v>4</v>
       </c>
-      <c r="J16" s="2">
-        <v>2</v>
-      </c>
       <c r="K16" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2">
         <v>0</v>
       </c>
       <c r="M16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2">
-        <v>1</v>
-      </c>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
+        <f>_xlfn.XLOOKUP(B17,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
@@ -1414,11 +3462,11 @@
         <v>1</v>
       </c>
       <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
         <v>4</v>
       </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
       <c r="I17" s="1">
         <v>0</v>
       </c>
@@ -1435,43 +3483,47 @@
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="1">
         <v>1</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
+        <f>_xlfn.XLOOKUP(B18,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
       <c r="E18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
         <v>3</v>
       </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2">
         <v>0</v>
@@ -1489,40 +3541,44 @@
         <v>0</v>
       </c>
       <c r="O18" s="2">
-        <v>2</v>
-      </c>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
+        <f>_xlfn.XLOOKUP(B19,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
         <v>3</v>
       </c>
-      <c r="H19" s="1">
-        <v>1</v>
-      </c>
       <c r="I19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="1">
         <v>0</v>
@@ -1540,42 +3596,46 @@
         <v>0</v>
       </c>
       <c r="O19" s="1">
-        <v>1</v>
-      </c>
-      <c r="P19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
+        <f>_xlfn.XLOOKUP(B20,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
       <c r="E20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
         <v>5</v>
       </c>
-      <c r="H20" s="2">
-        <v>1</v>
-      </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2">
         <v>0</v>
@@ -1593,26 +3653,30 @@
         <v>0</v>
       </c>
       <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
         <v>3</v>
       </c>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
+        <f>_xlfn.XLOOKUP(B21,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
@@ -1620,64 +3684,68 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
       <c r="I21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="1">
         <v>0</v>
       </c>
       <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
         <v>8</v>
       </c>
-      <c r="L21" s="1">
+      <c r="M21" s="1">
         <v>4</v>
       </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
       <c r="N21" s="1">
         <v>0</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
       </c>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
+        <f>_xlfn.XLOOKUP(B22,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="2">
+      <c r="E22" s="2">
         <v>3</v>
       </c>
-      <c r="E22" s="2">
-        <v>2</v>
-      </c>
       <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
         <v>5</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <v>3</v>
       </c>
-      <c r="H22" s="2">
-        <v>2</v>
-      </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2">
         <v>0</v>
@@ -1697,40 +3765,44 @@
       <c r="O22" s="2">
         <v>0</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
+        <f>_xlfn.XLOOKUP(B23,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>2</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
       <c r="E23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="1">
         <v>0</v>
@@ -1750,35 +3822,39 @@
       <c r="O23" s="1">
         <v>0</v>
       </c>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
+        <f>_xlfn.XLOOKUP(B24,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="2">
-        <v>0</v>
-      </c>
       <c r="E24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
@@ -1801,44 +3877,48 @@
       <c r="O24" s="2">
         <v>0</v>
       </c>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
+        <f>_xlfn.XLOOKUP(B25,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>4</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
       <c r="E25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="1">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1">
         <v>4</v>
       </c>
-      <c r="G25" s="1">
-        <v>2</v>
-      </c>
       <c r="H25" s="1">
         <v>2</v>
       </c>
       <c r="I25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -1850,26 +3930,30 @@
         <v>0</v>
       </c>
       <c r="O25" s="1">
-        <v>1</v>
-      </c>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
+        <f>_xlfn.XLOOKUP(B26,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
       <c r="E26" s="2">
         <v>0</v>
       </c>
@@ -1877,19 +3961,19 @@
         <v>0</v>
       </c>
       <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
         <v>4</v>
       </c>
-      <c r="H26" s="2">
-        <v>1</v>
-      </c>
       <c r="I26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2">
         <v>3</v>
       </c>
       <c r="K26" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2">
         <v>0</v>
@@ -1901,38 +3985,42 @@
         <v>0</v>
       </c>
       <c r="O26" s="2">
-        <v>1</v>
-      </c>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
+        <f>_xlfn.XLOOKUP(B27,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>6</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
         <v>3</v>
       </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
@@ -1952,31 +4040,35 @@
         <v>0</v>
       </c>
       <c r="O27" s="1">
-        <v>1</v>
-      </c>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
+        <f>_xlfn.XLOOKUP(B28,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>7</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
       <c r="E28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
         <v>2</v>
@@ -1985,7 +4077,7 @@
         <v>2</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="2">
         <v>0</v>
@@ -2000,41 +4092,45 @@
         <v>0</v>
       </c>
       <c r="N28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2">
         <v>1</v>
       </c>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P28" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
+        <f>_xlfn.XLOOKUP(B29,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
       <c r="E29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
         <v>5</v>
       </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
       <c r="I29" s="1">
         <v>0</v>
       </c>
@@ -2054,41 +4150,45 @@
         <v>0</v>
       </c>
       <c r="O29" s="1">
-        <v>1</v>
-      </c>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
+        <f>_xlfn.XLOOKUP(B30,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
       <c r="E30" s="2">
         <v>1</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2">
         <v>2</v>
       </c>
       <c r="H30" s="2">
+        <v>2</v>
+      </c>
+      <c r="I30" s="2">
         <v>3</v>
       </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
@@ -2105,26 +4205,30 @@
         <v>0</v>
       </c>
       <c r="O30" s="2">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
+        <f>_xlfn.XLOOKUP(B31,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>10</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
@@ -2135,61 +4239,65 @@
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="1">
         <v>0</v>
       </c>
       <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
         <v>9</v>
       </c>
-      <c r="L31" s="1">
+      <c r="M31" s="1">
         <v>3</v>
       </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
       <c r="N31" s="1">
         <v>0</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
       </c>
-      <c r="P31" s="1" t="s">
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
+        <f>_xlfn.XLOOKUP(B32,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="2">
+      <c r="E32" s="2">
         <v>3</v>
       </c>
-      <c r="E32" s="2">
-        <v>2</v>
-      </c>
       <c r="F32" s="2">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2">
         <v>7</v>
       </c>
-      <c r="G32" s="2">
+      <c r="H32" s="2">
         <v>3</v>
       </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
       <c r="I32" s="2">
         <v>0</v>
       </c>
@@ -2211,34 +4319,38 @@
       <c r="O32" s="2">
         <v>0</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="P32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
+        <f>_xlfn.XLOOKUP(B33,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>2</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
       <c r="E33" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" s="1">
         <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2262,46 +4374,50 @@
         <v>0</v>
       </c>
       <c r="O33" s="1">
-        <v>1</v>
-      </c>
-      <c r="P33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
+        <f>_xlfn.XLOOKUP(B34,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>3</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="2">
-        <v>0</v>
-      </c>
       <c r="E34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
         <v>4</v>
       </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
       <c r="K34" s="2">
         <v>0</v>
       </c>
@@ -2315,40 +4431,44 @@
         <v>0</v>
       </c>
       <c r="O34" s="2">
-        <v>2</v>
-      </c>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
+        <f>_xlfn.XLOOKUP(B35,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>4</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
       <c r="E35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" s="1">
         <v>0</v>
@@ -2366,46 +4486,50 @@
         <v>0</v>
       </c>
       <c r="O35" s="1">
-        <v>2</v>
-      </c>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
+        <f>_xlfn.XLOOKUP(B36,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>5</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="2">
-        <v>1</v>
-      </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
         <v>3</v>
       </c>
-      <c r="G36" s="2">
-        <v>2</v>
-      </c>
       <c r="H36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
         <v>3</v>
       </c>
-      <c r="J36" s="2">
-        <v>1</v>
-      </c>
       <c r="K36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2">
         <v>0</v>
@@ -2417,38 +4541,42 @@
         <v>0</v>
       </c>
       <c r="O36" s="2">
-        <v>1</v>
-      </c>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
+        <f>_xlfn.XLOOKUP(B37,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>6</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
       <c r="E37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1">
         <v>4</v>
       </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
@@ -2468,40 +4596,44 @@
         <v>0</v>
       </c>
       <c r="O37" s="1">
-        <v>1</v>
-      </c>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
+        <f>_xlfn.XLOOKUP(B38,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="2">
-        <v>0</v>
-      </c>
       <c r="E38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2">
         <v>2</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
@@ -2516,43 +4648,47 @@
         <v>0</v>
       </c>
       <c r="N38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2">
         <v>1</v>
       </c>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P38" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
+        <f>_xlfn.XLOOKUP(B39,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>8</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
       <c r="E39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
         <v>3</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>5</v>
       </c>
-      <c r="H39" s="1">
-        <v>2</v>
-      </c>
       <c r="I39" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" s="1">
         <v>0</v>
@@ -2570,40 +4706,44 @@
         <v>0</v>
       </c>
       <c r="O39" s="1">
-        <v>1</v>
-      </c>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
+        <f>_xlfn.XLOOKUP(B40,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>9</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="2">
-        <v>0</v>
-      </c>
       <c r="E40" s="2">
         <v>0</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
+        <v>2</v>
+      </c>
+      <c r="H40" s="2">
         <v>5</v>
       </c>
-      <c r="H40" s="2">
-        <v>1</v>
-      </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
@@ -2618,29 +4758,33 @@
         <v>0</v>
       </c>
       <c r="N40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="2">
-        <v>2</v>
-      </c>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
+        <f>_xlfn.XLOOKUP(B41,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>10</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="1">
-        <v>0</v>
-      </c>
       <c r="E41" s="1">
         <v>0</v>
       </c>
@@ -2648,64 +4792,68 @@
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="1">
         <v>0</v>
       </c>
       <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
         <v>8</v>
       </c>
-      <c r="L41" s="1">
+      <c r="M41" s="1">
         <v>3</v>
       </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
       <c r="N41" s="1">
         <v>0</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
       </c>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
+        <f>_xlfn.XLOOKUP(B42,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>1</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D42" s="2">
-        <v>2</v>
-      </c>
       <c r="E42" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42" s="2">
+        <v>2</v>
+      </c>
+      <c r="H42" s="2">
         <v>3</v>
       </c>
-      <c r="H42" s="2">
-        <v>1</v>
-      </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
@@ -2723,40 +4871,44 @@
         <v>0</v>
       </c>
       <c r="O42" s="2">
-        <v>1</v>
-      </c>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
+        <f>_xlfn.XLOOKUP(B43,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>2</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D43" s="1">
-        <v>2</v>
-      </c>
       <c r="E43" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
         <v>5</v>
       </c>
-      <c r="G43" s="1">
+      <c r="H43" s="1">
         <v>3</v>
       </c>
-      <c r="H43" s="1">
-        <v>2</v>
-      </c>
       <c r="I43" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" s="1">
         <v>0</v>
@@ -2776,41 +4928,45 @@
       <c r="O43" s="1">
         <v>0</v>
       </c>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
+        <f>_xlfn.XLOOKUP(B44,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>3</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="2">
-        <v>2</v>
-      </c>
       <c r="E44" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2">
         <v>4</v>
       </c>
-      <c r="G44" s="2">
-        <v>2</v>
-      </c>
       <c r="H44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="2">
         <v>1</v>
       </c>
       <c r="J44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="2">
         <v>0</v>
@@ -2827,29 +4983,33 @@
       <c r="O44" s="2">
         <v>0</v>
       </c>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P44" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
+        <f>_xlfn.XLOOKUP(B45,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>4</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
       <c r="E45" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -2858,14 +5018,14 @@
         <v>1</v>
       </c>
       <c r="I45" s="1">
+        <v>1</v>
+      </c>
+      <c r="J45" s="1">
         <v>4</v>
       </c>
-      <c r="J45" s="1">
+      <c r="K45" s="1">
         <v>3</v>
       </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
       <c r="L45" s="1">
         <v>0</v>
       </c>
@@ -2876,46 +5036,50 @@
         <v>0</v>
       </c>
       <c r="O45" s="1">
-        <v>2</v>
-      </c>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
+        <f>_xlfn.XLOOKUP(B46,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>5</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
       <c r="E46" s="2">
         <v>0</v>
       </c>
       <c r="F46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="2">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2">
         <v>4</v>
       </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
       <c r="I46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>
       </c>
       <c r="K46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2">
         <v>0</v>
@@ -2927,41 +5091,45 @@
         <v>0</v>
       </c>
       <c r="O46" s="2">
-        <v>1</v>
-      </c>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
+        <f>_xlfn.XLOOKUP(B47,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>6</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D47" s="1">
-        <v>1</v>
-      </c>
       <c r="E47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
         <v>3</v>
       </c>
-      <c r="G47" s="1">
-        <v>1</v>
-      </c>
       <c r="H47" s="1">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1">
         <v>3</v>
       </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
       <c r="J47" s="1">
         <v>0</v>
       </c>
@@ -2978,40 +5146,44 @@
         <v>0</v>
       </c>
       <c r="O47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
         <v>3</v>
       </c>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
+        <f>_xlfn.XLOOKUP(B48,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>7</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="2">
-        <v>0</v>
-      </c>
       <c r="E48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
       </c>
       <c r="G48" s="2">
+        <v>1</v>
+      </c>
+      <c r="H48" s="2">
         <v>3</v>
       </c>
-      <c r="H48" s="2">
-        <v>1</v>
-      </c>
       <c r="I48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="2">
         <v>0</v>
@@ -3031,40 +5203,44 @@
       <c r="O48" s="2">
         <v>0</v>
       </c>
-      <c r="P48" s="2" t="s">
+      <c r="P48" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q48" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
+        <f>_xlfn.XLOOKUP(B49,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>8</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
       <c r="E49" s="1">
         <v>1</v>
       </c>
       <c r="F49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="1">
         <v>0</v>
@@ -3079,43 +5255,47 @@
         <v>0</v>
       </c>
       <c r="N49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="1">
+        <v>1</v>
+      </c>
+      <c r="P49" s="1">
         <v>3</v>
       </c>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
+        <f>_xlfn.XLOOKUP(B50,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>9</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D50" s="2">
-        <v>0</v>
-      </c>
       <c r="E50" s="2">
         <v>0</v>
       </c>
       <c r="F50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2">
         <v>2</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" s="2">
         <v>0</v>
@@ -3135,24 +5315,28 @@
       <c r="O50" s="2">
         <v>0</v>
       </c>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P50" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
+        <f>_xlfn.XLOOKUP(B51,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>10</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
       <c r="E51" s="1">
         <v>0</v>
       </c>
@@ -3160,50 +5344,54 @@
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="1">
         <v>0</v>
       </c>
       <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1">
         <v>11</v>
       </c>
-      <c r="L51" s="1">
+      <c r="M51" s="1">
         <v>8</v>
       </c>
-      <c r="M51" s="1">
-        <v>0</v>
-      </c>
       <c r="N51" s="1">
         <v>0</v>
       </c>
       <c r="O51" s="1">
         <v>0</v>
       </c>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
+        <f>_xlfn.XLOOKUP(B52,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>1</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D52" s="2">
-        <v>1</v>
-      </c>
       <c r="E52" s="2">
         <v>1</v>
       </c>
@@ -3211,11 +5399,11 @@
         <v>1</v>
       </c>
       <c r="G52" s="2">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2">
         <v>3</v>
       </c>
-      <c r="H52" s="2">
-        <v>0</v>
-      </c>
       <c r="I52" s="2">
         <v>0</v>
       </c>
@@ -3237,38 +5425,42 @@
       <c r="O52" s="2">
         <v>0</v>
       </c>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P52" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
+        <f>_xlfn.XLOOKUP(B53,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>2</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D53" s="1">
+      <c r="E53" s="1">
         <v>3</v>
       </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
       <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
         <v>5</v>
       </c>
-      <c r="G53" s="1">
-        <v>2</v>
-      </c>
       <c r="H53" s="1">
         <v>2</v>
       </c>
       <c r="I53" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
@@ -3280,45 +5472,49 @@
         <v>0</v>
       </c>
       <c r="M53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="1">
-        <v>1</v>
-      </c>
-      <c r="P53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P53" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Q53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
+        <f>_xlfn.XLOOKUP(B54,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>3</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="2">
-        <v>2</v>
-      </c>
       <c r="E54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2">
         <v>4</v>
       </c>
       <c r="H54" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I54" s="2">
         <v>2</v>
@@ -3327,7 +5523,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2">
         <v>0</v>
@@ -3339,44 +5535,48 @@
         <v>0</v>
       </c>
       <c r="O54" s="2">
-        <v>1</v>
-      </c>
-      <c r="P54" s="2"/>
-      <c r="Q54" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
+        <f>_xlfn.XLOOKUP(B55,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>4</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="1">
-        <v>2</v>
-      </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="1">
         <v>3</v>
       </c>
       <c r="H55" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" s="1">
+        <v>1</v>
+      </c>
+      <c r="J55" s="1">
         <v>4</v>
       </c>
-      <c r="J55" s="1">
-        <v>0</v>
-      </c>
       <c r="K55" s="1">
         <v>0</v>
       </c>
@@ -3392,44 +5592,48 @@
       <c r="O55" s="1">
         <v>0</v>
       </c>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
+        <f>_xlfn.XLOOKUP(B56,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>5</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D56" s="2">
-        <v>2</v>
-      </c>
       <c r="E56" s="2">
         <v>2</v>
       </c>
       <c r="F56" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G56" s="2">
         <v>4</v>
       </c>
       <c r="H56" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
         <v>3</v>
       </c>
-      <c r="J56" s="2">
-        <v>1</v>
-      </c>
       <c r="K56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2">
         <v>0</v>
@@ -3441,40 +5645,44 @@
         <v>0</v>
       </c>
       <c r="O56" s="2">
-        <v>2</v>
-      </c>
-      <c r="P56" s="2"/>
-      <c r="Q56" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
+        <f>_xlfn.XLOOKUP(B57,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>6</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
       <c r="E57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" s="1">
         <v>5</v>
       </c>
-      <c r="H57" s="1">
-        <v>2</v>
-      </c>
       <c r="I57" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J57" s="1">
         <v>0</v>
@@ -3492,26 +5700,30 @@
         <v>0</v>
       </c>
       <c r="O57" s="1">
-        <v>1</v>
-      </c>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
+        <f>_xlfn.XLOOKUP(B58,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>7</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
       <c r="E58" s="2">
         <v>0</v>
       </c>
@@ -3519,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="G58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="2">
         <v>0</v>
@@ -3543,42 +5755,46 @@
         <v>0</v>
       </c>
       <c r="O58" s="2">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2">
         <v>3</v>
       </c>
-      <c r="P58" s="2" t="s">
+      <c r="Q58" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
+        <f>_xlfn.XLOOKUP(B59,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>8</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D59" s="1">
-        <v>1</v>
-      </c>
       <c r="E59" s="1">
         <v>1</v>
       </c>
       <c r="F59" s="1">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1">
         <v>3</v>
       </c>
-      <c r="G59" s="1">
+      <c r="H59" s="1">
         <v>5</v>
       </c>
-      <c r="H59" s="1">
-        <v>1</v>
-      </c>
       <c r="I59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="1">
         <v>0</v>
@@ -3593,40 +5809,44 @@
         <v>0</v>
       </c>
       <c r="N59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" s="1">
+        <v>1</v>
+      </c>
+      <c r="P59" s="1">
         <v>3</v>
       </c>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
+        <f>_xlfn.XLOOKUP(B60,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>9</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
       <c r="E60" s="2">
         <v>0</v>
       </c>
       <c r="F60" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="2">
         <v>0</v>
@@ -3644,29 +5864,33 @@
         <v>0</v>
       </c>
       <c r="N60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" s="2">
         <v>1</v>
       </c>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P60" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
+        <f>_xlfn.XLOOKUP(B61,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>10</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
@@ -3674,25 +5898,25 @@
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="1">
         <v>0</v>
       </c>
       <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
         <v>5</v>
       </c>
-      <c r="L61" s="1">
-        <v>1</v>
-      </c>
       <c r="M61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" s="1">
         <v>0</v>
@@ -3700,40 +5924,44 @@
       <c r="O61" s="1">
         <v>0</v>
       </c>
-      <c r="P61" s="1" t="s">
+      <c r="P61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Q61" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
+        <f>_xlfn.XLOOKUP(B62,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>1</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E62" s="2">
         <v>3</v>
       </c>
-      <c r="E62" s="2">
-        <v>0</v>
-      </c>
       <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2">
         <v>6</v>
       </c>
-      <c r="G62" s="2">
-        <v>2</v>
-      </c>
       <c r="H62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="2">
         <v>0</v>
@@ -3745,48 +5973,52 @@
         <v>0</v>
       </c>
       <c r="M62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" s="2">
-        <v>1</v>
-      </c>
-      <c r="P62" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R62" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
+        <f>_xlfn.XLOOKUP(B63,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>2</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D63" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="1">
+        <v>2</v>
+      </c>
+      <c r="G63" s="1">
         <v>4</v>
       </c>
-      <c r="G63" s="1">
+      <c r="H63" s="1">
         <v>3</v>
       </c>
-      <c r="H63" s="1">
-        <v>1</v>
-      </c>
       <c r="I63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="1">
         <v>0</v>
@@ -3798,49 +6030,53 @@
         <v>0</v>
       </c>
       <c r="M63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" s="1">
-        <v>1</v>
-      </c>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
+        <f>_xlfn.XLOOKUP(B64,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>3</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E64" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G64" s="2">
         <v>4</v>
       </c>
       <c r="H64" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I64" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" s="2">
         <v>0</v>
@@ -3855,43 +6091,47 @@
         <v>0</v>
       </c>
       <c r="O64" s="2">
-        <v>1</v>
-      </c>
-      <c r="P64" s="2"/>
-      <c r="Q64" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
+        <f>_xlfn.XLOOKUP(B65,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>4</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
         <v>4</v>
       </c>
-      <c r="H65" s="1">
-        <v>2</v>
-      </c>
       <c r="I65" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
@@ -3908,46 +6148,50 @@
       <c r="O65" s="1">
         <v>0</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
+        <f>_xlfn.XLOOKUP(B66,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>5</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E66" s="2">
         <v>1</v>
       </c>
       <c r="F66" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G66" s="2">
         <v>4</v>
       </c>
       <c r="H66" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="2">
         <v>1</v>
       </c>
       <c r="K66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2">
         <v>0</v>
@@ -3959,25 +6203,29 @@
         <v>0</v>
       </c>
       <c r="O66" s="2">
-        <v>2</v>
-      </c>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
+        <f>_xlfn.XLOOKUP(B67,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>6</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D67" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3986,13 +6234,13 @@
         <v>1</v>
       </c>
       <c r="G67" s="1">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1">
         <v>3</v>
       </c>
-      <c r="H67" s="1">
-        <v>2</v>
-      </c>
       <c r="I67" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" s="1">
         <v>0</v>
@@ -4007,44 +6255,48 @@
         <v>0</v>
       </c>
       <c r="N67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="1">
+        <v>1</v>
+      </c>
+      <c r="P67" s="1">
         <v>3</v>
       </c>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
+        <f>_xlfn.XLOOKUP(B68,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>7</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2">
+        <v>2</v>
+      </c>
+      <c r="H68" s="2">
         <v>4</v>
       </c>
-      <c r="H68" s="2">
+      <c r="I68" s="2">
         <v>3</v>
       </c>
-      <c r="I68" s="2">
-        <v>0</v>
-      </c>
       <c r="J68" s="2">
         <v>0</v>
       </c>
@@ -4061,37 +6313,41 @@
         <v>0</v>
       </c>
       <c r="O68" s="2">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2">
         <v>3</v>
       </c>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
+        <f>_xlfn.XLOOKUP(B69,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>8</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D69" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G69" s="1">
         <v>2</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
@@ -4109,40 +6365,44 @@
         <v>0</v>
       </c>
       <c r="N69" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="1">
-        <v>0</v>
-      </c>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="P69" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
+        <f>_xlfn.XLOOKUP(B70,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>9</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D70" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="E70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G70" s="2">
         <v>2</v>
       </c>
       <c r="H70" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" s="2">
         <v>0</v>
@@ -4160,27 +6420,31 @@
         <v>0</v>
       </c>
       <c r="N70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" s="2">
+        <v>1</v>
+      </c>
+      <c r="P70" s="2">
         <v>3</v>
       </c>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
+        <f>_xlfn.XLOOKUP(B71,[1]DimPlayers!$B$2:$B$11,[1]DimPlayers!$A$2:$A$11)</f>
         <v>10</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E71" s="1">
@@ -4193,31 +6457,34 @@
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="1">
         <v>0</v>
       </c>
       <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
         <v>10</v>
       </c>
-      <c r="L71" s="1">
+      <c r="M71" s="1">
         <v>5</v>
       </c>
-      <c r="M71" s="1">
-        <v>0</v>
-      </c>
       <c r="N71" s="1">
         <v>0</v>
       </c>
       <c r="O71" s="1">
         <v>0</v>
       </c>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1">
+      <c r="P71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -8,21 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6D3AACD-61D5-4E20-9BC2-4A4EF64A7A83}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBCE0370-8EA5-4CDF-B1BE-CE4B695694F2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
-    <sheet name="FactTable" sheetId="2" r:id="rId2"/>
+    <sheet name="FactTable" sheetId="2" r:id="rId1"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId2"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="46">
   <si>
     <t>Maplewood HS</t>
   </si>
@@ -182,21 +178,6 @@
   <si>
     <t>Lauren Scott</t>
   </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Column Labels</t>
-  </si>
-  <si>
-    <t>(blank)</t>
-  </si>
-  <si>
-    <t>Count of PenType</t>
-  </si>
 </sst>
 </file>
 
@@ -268,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -279,11 +260,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,1619 +372,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Chris Napoli" refreshedDate="46083.53809814815" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="70" xr:uid="{9B219841-7E8E-46DC-9F7F-1EF254B500FA}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:R71" sheet="FactTable"/>
-  </cacheSource>
-  <cacheFields count="18">
-    <cacheField name="PlayerID" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
-    </cacheField>
-    <cacheField name="F_PlayerName" numFmtId="0">
-      <sharedItems count="10">
-        <s v="Olivia Hart"/>
-        <s v="Mia Russo"/>
-        <s v="Emma Torres"/>
-        <s v="Sophie Kim"/>
-        <s v="Ava Nguyen"/>
-        <s v="Chloe Banks"/>
-        <s v="Riley Patel"/>
-        <s v="Jenna Walsh"/>
-        <s v="Natalie Cruz"/>
-        <s v="Lauren Scott"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Date" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="OpponentName" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Goals" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="Assists" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
-    </cacheField>
-    <cacheField name="Shots" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="7"/>
-    </cacheField>
-    <cacheField name="GBs" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="5"/>
-    </cacheField>
-    <cacheField name="TOs" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="DrawAtts" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="4"/>
-    </cacheField>
-    <cacheField name="DrawControls" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="ShotsFaced" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="11"/>
-    </cacheField>
-    <cacheField name="Saves" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="8"/>
-    </cacheField>
-    <cacheField name="WomanUpGoals" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="WomanDownGoals" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="CTOs" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="PenType" numFmtId="0">
-      <sharedItems containsBlank="1" count="5">
-        <m/>
-        <s v="Green"/>
-        <s v="Yellow"/>
-        <s v="12m"/>
-        <s v="Red"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="MinsServed" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="70">
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="1"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <s v="2025-03-08"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <s v="2025-03-15"/>
-    <s v="Lakewood HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="8"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="2"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <s v="2025-03-22"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="9"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="7"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <s v="2025-03-29"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="8"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <s v="2025-04-05"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="11"/>
-    <n v="8"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="2"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <s v="2025-04-12"/>
-    <s v="Cedar Falls HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="6"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <s v="2025-04-19"/>
-    <s v="Maplewood HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="10"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F71C58A-B4F5-465D-857D-A0DA0D629E32}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="16"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of PenType" fld="16" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2327,219 +690,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FECCF03-21CB-4BCE-B5AE-16126AAD8F80}">
-  <dimension ref="A3:G15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="6">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6">
-        <v>1</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="6">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6">
-        <v>2</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="6">
-        <v>3</v>
-      </c>
-      <c r="C15" s="6">
-        <v>4</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6">
-        <v>4</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{675130FE-5529-48C3-883E-D019D34D4137}">
   <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBCE0370-8EA5-4CDF-B1BE-CE4B695694F2}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F071C894-D995-4F03-91D1-2D7339AE29AE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
+    <workbookView xWindow="57480" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
   <sheets>
-    <sheet name="FactTable" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="FactTable" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="3" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="54">
   <si>
     <t>Maplewood HS</t>
   </si>
@@ -178,12 +182,39 @@
   <si>
     <t>Lauren Scott</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Goals</t>
+  </si>
+  <si>
+    <t>Sum of Assists</t>
+  </si>
+  <si>
+    <t>Sum of GBs</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>PPG</t>
+  </si>
+  <si>
+    <t>Assist</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,8 +232,16 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,8 +260,14 @@
         <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -245,11 +290,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -260,6 +323,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -372,6 +445,1597 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Chris Napoli" refreshedDate="46084.654355555555" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="70" xr:uid="{45BECAE6-F96A-464F-B8E1-6CE7A28CF657}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:R71" sheet="FactTable"/>
+  </cacheSource>
+  <cacheFields count="18">
+    <cacheField name="PlayerID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
+    </cacheField>
+    <cacheField name="F_PlayerName" numFmtId="0">
+      <sharedItems count="10">
+        <s v="Olivia Hart"/>
+        <s v="Mia Russo"/>
+        <s v="Emma Torres"/>
+        <s v="Sophie Kim"/>
+        <s v="Ava Nguyen"/>
+        <s v="Chloe Banks"/>
+        <s v="Riley Patel"/>
+        <s v="Jenna Walsh"/>
+        <s v="Natalie Cruz"/>
+        <s v="Lauren Scott"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Date" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="OpponentName" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Goals" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
+    </cacheField>
+    <cacheField name="Assists" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
+    </cacheField>
+    <cacheField name="Shots" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="7"/>
+    </cacheField>
+    <cacheField name="GBs" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="5"/>
+    </cacheField>
+    <cacheField name="TOs" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
+    </cacheField>
+    <cacheField name="DrawAtts" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="4"/>
+    </cacheField>
+    <cacheField name="DrawControls" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
+    </cacheField>
+    <cacheField name="ShotsFaced" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="11"/>
+    </cacheField>
+    <cacheField name="Saves" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="8"/>
+    </cacheField>
+    <cacheField name="WomanUpGoals" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="WomanDownGoals" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="CTOs" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
+    </cacheField>
+    <cacheField name="PenType" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="MinsServed" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="70">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <s v="Green"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-03-08"/>
+    <s v="Riverside HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="Green"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-03-15"/>
+    <s v="Lakewood HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <s v="Yellow"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-03-22"/>
+    <s v="Northview HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="9"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <s v="Green"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="7"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <s v="12m"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="Yellow"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-03-29"/>
+    <s v="Summit Academy"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="8"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <s v="Green"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-04-05"/>
+    <s v="Eastbrook HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="11"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="12m"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="3"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="5"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <s v="Yellow"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-04-12"/>
+    <s v="Cedar Falls HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="5"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <s v="12m"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="6"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="Yellow"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <s v="Red"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="4"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="3"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <m/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="2025-04-19"/>
+    <s v="Maplewood HS"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="10"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <n v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93B1F2E5-6101-4B7D-8463-217B5EDC7EF7}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of Goals" fld="4" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Assists" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Sum of GBs" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -690,6 +2354,513 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBA3C68-2291-42D7-93ED-B36167695E1B}">
+  <dimension ref="A3:L14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" hidden="1" customWidth="1"/>
+    <col min="5" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="6">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6">
+        <v>20</v>
+      </c>
+      <c r="E4" s="6">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6">
+        <v>20</v>
+      </c>
+      <c r="H4" s="11">
+        <f>+I4/7</f>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="I4">
+        <f>+SUM(E4:F4)</f>
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <f>+E4</f>
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <f>+F4</f>
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <f>+G4</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6">
+        <v>21</v>
+      </c>
+      <c r="E5" s="6">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6">
+        <v>21</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" ref="H5:H13" si="0">+I5/7</f>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I13" si="1">+SUM(E5:F5)</f>
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <f t="shared" ref="J5:J13" si="2">+E5</f>
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <f t="shared" ref="K5:K13" si="3">+F5</f>
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ref="L5:L13" si="4">+G5</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="6">
+        <v>8</v>
+      </c>
+      <c r="C6" s="6">
+        <v>8</v>
+      </c>
+      <c r="D6" s="6">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6">
+        <v>8</v>
+      </c>
+      <c r="F6" s="6">
+        <v>8</v>
+      </c>
+      <c r="G6" s="6">
+        <v>18</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="0"/>
+        <v>2.2857142857142856</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="6">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6">
+        <v>24</v>
+      </c>
+      <c r="E7" s="6">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6">
+        <v>3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>24</v>
+      </c>
+      <c r="H7" s="11">
+        <f t="shared" si="0"/>
+        <v>1.2857142857142858</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>6</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>6</v>
+      </c>
+      <c r="H8" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6">
+        <v>8</v>
+      </c>
+      <c r="D9" s="6">
+        <v>10</v>
+      </c>
+      <c r="E9" s="6">
+        <v>7</v>
+      </c>
+      <c r="F9" s="6">
+        <v>8</v>
+      </c>
+      <c r="G9" s="6">
+        <v>10</v>
+      </c>
+      <c r="H9" s="11">
+        <f t="shared" si="0"/>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="6">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>21</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2</v>
+      </c>
+      <c r="G10" s="6">
+        <v>21</v>
+      </c>
+      <c r="H10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="4"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="6">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6">
+        <v>5</v>
+      </c>
+      <c r="D11" s="6">
+        <v>17</v>
+      </c>
+      <c r="E11" s="6">
+        <v>14</v>
+      </c>
+      <c r="F11" s="6">
+        <v>5</v>
+      </c>
+      <c r="G11" s="6">
+        <v>17</v>
+      </c>
+      <c r="H11" s="11">
+        <f t="shared" si="0"/>
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="6">
+        <v>3</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6">
+        <v>16</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6">
+        <v>2</v>
+      </c>
+      <c r="G12" s="6">
+        <v>16</v>
+      </c>
+      <c r="H12" s="11">
+        <f t="shared" si="0"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6">
+        <v>6</v>
+      </c>
+      <c r="C13" s="6">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6">
+        <v>17</v>
+      </c>
+      <c r="E13" s="6">
+        <v>6</v>
+      </c>
+      <c r="F13" s="6">
+        <v>9</v>
+      </c>
+      <c r="G13" s="6">
+        <v>17</v>
+      </c>
+      <c r="H13" s="11">
+        <f t="shared" si="0"/>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="6">
+        <v>57</v>
+      </c>
+      <c r="C14" s="6">
+        <v>44</v>
+      </c>
+      <c r="D14" s="6">
+        <v>170</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="I4:I13" formulaRange="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{675130FE-5529-48C3-883E-D019D34D4137}">
   <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F071C894-D995-4F03-91D1-2D7339AE29AE}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B0F9D27-3A12-462D-A569-EF3945346ED1}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
+    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId4"/>
+    <pivotCache cacheId="4" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="50">
   <si>
     <t>Maplewood HS</t>
   </si>
@@ -194,27 +194,15 @@
   <si>
     <t>Sum of Assists</t>
   </si>
-  <si>
-    <t>Sum of GBs</t>
-  </si>
-  <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>PPG</t>
-  </si>
-  <si>
-    <t>Assist</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +219,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -267,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -299,20 +294,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,14 +315,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -471,7 +456,15 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Date" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="7">
+        <s v="2025-03-08"/>
+        <s v="2025-03-15"/>
+        <s v="2025-03-22"/>
+        <s v="2025-03-29"/>
+        <s v="2025-04-05"/>
+        <s v="2025-04-12"/>
+        <s v="2025-04-19"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="OpponentName" numFmtId="0">
       <sharedItems/>
@@ -532,7 +525,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -552,7 +545,7 @@
   <r>
     <n v="2"/>
     <x v="1"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="0"/>
     <n v="2"/>
@@ -572,7 +565,7 @@
   <r>
     <n v="3"/>
     <x v="2"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="0"/>
     <n v="2"/>
@@ -592,7 +585,7 @@
   <r>
     <n v="4"/>
     <x v="3"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="2"/>
     <n v="1"/>
@@ -612,7 +605,7 @@
   <r>
     <n v="5"/>
     <x v="4"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -632,7 +625,7 @@
   <r>
     <n v="6"/>
     <x v="5"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="1"/>
     <n v="0"/>
@@ -652,7 +645,7 @@
   <r>
     <n v="7"/>
     <x v="6"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -672,7 +665,7 @@
   <r>
     <n v="8"/>
     <x v="7"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -692,7 +685,7 @@
   <r>
     <n v="9"/>
     <x v="8"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -712,7 +705,7 @@
   <r>
     <n v="10"/>
     <x v="9"/>
-    <s v="2025-03-08"/>
+    <x v="0"/>
     <s v="Riverside HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -732,7 +725,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="2"/>
     <n v="0"/>
@@ -752,7 +745,7 @@
   <r>
     <n v="2"/>
     <x v="1"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -772,7 +765,7 @@
   <r>
     <n v="3"/>
     <x v="2"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="2"/>
     <n v="1"/>
@@ -792,7 +785,7 @@
   <r>
     <n v="4"/>
     <x v="3"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="0"/>
     <n v="2"/>
@@ -812,7 +805,7 @@
   <r>
     <n v="5"/>
     <x v="4"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="2"/>
     <n v="1"/>
@@ -832,7 +825,7 @@
   <r>
     <n v="6"/>
     <x v="5"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -852,7 +845,7 @@
   <r>
     <n v="7"/>
     <x v="6"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="1"/>
     <n v="0"/>
@@ -872,7 +865,7 @@
   <r>
     <n v="8"/>
     <x v="7"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -892,7 +885,7 @@
   <r>
     <n v="9"/>
     <x v="8"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="0"/>
     <n v="1"/>
@@ -912,7 +905,7 @@
   <r>
     <n v="10"/>
     <x v="9"/>
-    <s v="2025-03-15"/>
+    <x v="1"/>
     <s v="Lakewood HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -932,7 +925,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="3"/>
     <n v="2"/>
@@ -952,7 +945,7 @@
   <r>
     <n v="2"/>
     <x v="1"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="0"/>
     <n v="1"/>
@@ -972,7 +965,7 @@
   <r>
     <n v="3"/>
     <x v="2"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="0"/>
     <n v="2"/>
@@ -992,7 +985,7 @@
   <r>
     <n v="4"/>
     <x v="3"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="1"/>
     <n v="2"/>
@@ -1012,7 +1005,7 @@
   <r>
     <n v="5"/>
     <x v="4"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1032,7 +1025,7 @@
   <r>
     <n v="6"/>
     <x v="5"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1052,7 +1045,7 @@
   <r>
     <n v="7"/>
     <x v="6"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="1"/>
     <n v="0"/>
@@ -1072,7 +1065,7 @@
   <r>
     <n v="8"/>
     <x v="7"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="1"/>
     <n v="0"/>
@@ -1092,7 +1085,7 @@
   <r>
     <n v="9"/>
     <x v="8"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -1112,7 +1105,7 @@
   <r>
     <n v="10"/>
     <x v="9"/>
-    <s v="2025-03-22"/>
+    <x v="2"/>
     <s v="Northview HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1132,7 +1125,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="3"/>
     <n v="2"/>
@@ -1152,7 +1145,7 @@
   <r>
     <n v="2"/>
     <x v="1"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="0"/>
     <n v="2"/>
@@ -1172,7 +1165,7 @@
   <r>
     <n v="3"/>
     <x v="2"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="0"/>
     <n v="2"/>
@@ -1192,7 +1185,7 @@
   <r>
     <n v="4"/>
     <x v="3"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="1"/>
     <n v="0"/>
@@ -1212,7 +1205,7 @@
   <r>
     <n v="5"/>
     <x v="4"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="1"/>
     <n v="0"/>
@@ -1232,7 +1225,7 @@
   <r>
     <n v="6"/>
     <x v="5"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="1"/>
     <n v="0"/>
@@ -1252,7 +1245,7 @@
   <r>
     <n v="7"/>
     <x v="6"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="0"/>
     <n v="1"/>
@@ -1272,7 +1265,7 @@
   <r>
     <n v="8"/>
     <x v="7"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="1"/>
     <n v="0"/>
@@ -1292,7 +1285,7 @@
   <r>
     <n v="9"/>
     <x v="8"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="0"/>
     <n v="0"/>
@@ -1312,7 +1305,7 @@
   <r>
     <n v="10"/>
     <x v="9"/>
-    <s v="2025-03-29"/>
+    <x v="3"/>
     <s v="Summit Academy"/>
     <n v="0"/>
     <n v="0"/>
@@ -1332,7 +1325,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="2"/>
     <n v="0"/>
@@ -1352,7 +1345,7 @@
   <r>
     <n v="2"/>
     <x v="1"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="2"/>
     <n v="0"/>
@@ -1372,7 +1365,7 @@
   <r>
     <n v="3"/>
     <x v="2"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="2"/>
     <n v="0"/>
@@ -1392,7 +1385,7 @@
   <r>
     <n v="4"/>
     <x v="3"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="0"/>
     <n v="2"/>
@@ -1412,7 +1405,7 @@
   <r>
     <n v="5"/>
     <x v="4"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1432,7 +1425,7 @@
   <r>
     <n v="6"/>
     <x v="5"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="1"/>
     <n v="0"/>
@@ -1452,7 +1445,7 @@
   <r>
     <n v="7"/>
     <x v="6"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="0"/>
     <n v="1"/>
@@ -1472,7 +1465,7 @@
   <r>
     <n v="8"/>
     <x v="7"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -1492,7 +1485,7 @@
   <r>
     <n v="9"/>
     <x v="8"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1512,7 +1505,7 @@
   <r>
     <n v="10"/>
     <x v="9"/>
-    <s v="2025-04-05"/>
+    <x v="4"/>
     <s v="Eastbrook HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1532,7 +1525,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -1552,7 +1545,7 @@
   <r>
     <n v="2"/>
     <x v="1"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="3"/>
     <n v="0"/>
@@ -1572,7 +1565,7 @@
   <r>
     <n v="3"/>
     <x v="2"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="2"/>
     <n v="1"/>
@@ -1592,7 +1585,7 @@
   <r>
     <n v="4"/>
     <x v="3"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="2"/>
     <n v="2"/>
@@ -1612,7 +1605,7 @@
   <r>
     <n v="5"/>
     <x v="4"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="2"/>
     <n v="2"/>
@@ -1632,7 +1625,7 @@
   <r>
     <n v="6"/>
     <x v="5"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="0"/>
     <n v="1"/>
@@ -1652,7 +1645,7 @@
   <r>
     <n v="7"/>
     <x v="6"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1672,7 +1665,7 @@
   <r>
     <n v="8"/>
     <x v="7"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -1692,7 +1685,7 @@
   <r>
     <n v="9"/>
     <x v="8"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1712,7 +1705,7 @@
   <r>
     <n v="10"/>
     <x v="9"/>
-    <s v="2025-04-12"/>
+    <x v="5"/>
     <s v="Cedar Falls HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1732,7 +1725,7 @@
   <r>
     <n v="1"/>
     <x v="0"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="3"/>
     <n v="0"/>
@@ -1752,7 +1745,7 @@
   <r>
     <n v="2"/>
     <x v="1"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="1"/>
     <n v="2"/>
@@ -1772,7 +1765,7 @@
   <r>
     <n v="3"/>
     <x v="2"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="2"/>
     <n v="0"/>
@@ -1792,7 +1785,7 @@
   <r>
     <n v="4"/>
     <x v="3"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1812,7 +1805,7 @@
   <r>
     <n v="5"/>
     <x v="4"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -1832,7 +1825,7 @@
   <r>
     <n v="6"/>
     <x v="5"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="1"/>
     <n v="1"/>
@@ -1852,7 +1845,7 @@
   <r>
     <n v="7"/>
     <x v="6"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="1"/>
     <n v="0"/>
@@ -1872,7 +1865,7 @@
   <r>
     <n v="8"/>
     <x v="7"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="1"/>
     <n v="0"/>
@@ -1892,7 +1885,7 @@
   <r>
     <n v="9"/>
     <x v="8"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="1"/>
     <n v="0"/>
@@ -1912,7 +1905,7 @@
   <r>
     <n v="10"/>
     <x v="9"/>
-    <s v="2025-04-19"/>
+    <x v="6"/>
     <s v="Maplewood HS"/>
     <n v="0"/>
     <n v="0"/>
@@ -1933,8 +1926,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93B1F2E5-6101-4B7D-8463-217B5EDC7EF7}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93B1F2E5-6101-4B7D-8463-217B5EDC7EF7}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -1952,12 +1945,23 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2010,21 +2014,17 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="3">
+  <colItems count="2">
     <i>
       <x/>
     </i>
     <i i="1">
       <x v="1"/>
     </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
   </colItems>
-  <dataFields count="3">
+  <dataFields count="2">
     <dataField name="Sum of Goals" fld="4" baseField="0" baseItem="0"/>
     <dataField name="Sum of Assists" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Sum of GBs" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -2355,18 +2355,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBA3C68-2291-42D7-93ED-B36167695E1B}">
-  <dimension ref="A3:L14"/>
+  <dimension ref="A3:F14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.26953125" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="13.6328125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" hidden="1" customWidth="1"/>
-    <col min="5" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
@@ -2376,35 +2387,14 @@
       <c r="C3" t="s">
         <v>49</v>
       </c>
-      <c r="D3" t="s">
-        <v>50</v>
+      <c r="D3" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>40</v>
       </c>
@@ -2415,39 +2405,17 @@
         <v>4</v>
       </c>
       <c r="D4" s="6">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E4" s="6">
-        <v>6</v>
-      </c>
-      <c r="F4" s="6">
         <v>4</v>
       </c>
-      <c r="G4" s="6">
-        <v>20</v>
-      </c>
-      <c r="H4" s="11">
-        <f>+I4/7</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="I4">
-        <f>+SUM(E4:F4)</f>
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <f>+E4</f>
-        <v>6</v>
-      </c>
-      <c r="K4">
-        <f>+F4</f>
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <f>+G4</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="F4" s="8">
+        <f>+D4/SUM(D4:E4)</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
@@ -2458,39 +2426,17 @@
         <v>3</v>
       </c>
       <c r="D5" s="6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E5" s="6">
-        <v>5</v>
-      </c>
-      <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="G5" s="6">
-        <v>21</v>
-      </c>
-      <c r="H5" s="11">
-        <f t="shared" ref="H5:H13" si="0">+I5/7</f>
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="I5">
-        <f t="shared" ref="I5:I13" si="1">+SUM(E5:F5)</f>
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <f t="shared" ref="J5:J13" si="2">+E5</f>
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <f t="shared" ref="K5:K13" si="3">+F5</f>
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <f t="shared" ref="L5:L13" si="4">+G5</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="F5" s="8">
+        <f t="shared" ref="F5:F13" si="0">+D5/SUM(D5:E5)</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>38</v>
       </c>
@@ -2501,39 +2447,17 @@
         <v>8</v>
       </c>
       <c r="D6" s="6">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E6" s="6">
         <v>8</v>
       </c>
-      <c r="F6" s="6">
-        <v>8</v>
-      </c>
-      <c r="G6" s="6">
-        <v>18</v>
-      </c>
-      <c r="H6" s="11">
+      <c r="F6" s="8">
         <f t="shared" si="0"/>
-        <v>2.2857142857142856</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="4"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
@@ -2544,39 +2468,17 @@
         <v>3</v>
       </c>
       <c r="D7" s="6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E7" s="6">
-        <v>6</v>
-      </c>
-      <c r="F7" s="6">
         <v>3</v>
       </c>
-      <c r="G7" s="6">
-        <v>24</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="F7" s="8">
         <f t="shared" si="0"/>
-        <v>1.2857142857142858</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="4"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>45</v>
       </c>
@@ -2587,39 +2489,17 @@
         <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E8" s="6">
         <v>0</v>
       </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>6</v>
-      </c>
-      <c r="H8" s="11">
+      <c r="F8" s="8" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
@@ -2630,39 +2510,17 @@
         <v>8</v>
       </c>
       <c r="D9" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6">
-        <v>7</v>
-      </c>
-      <c r="F9" s="6">
         <v>8</v>
       </c>
-      <c r="G9" s="6">
-        <v>10</v>
-      </c>
-      <c r="H9" s="11">
+      <c r="F9" s="8">
         <f t="shared" si="0"/>
-        <v>2.1428571428571428</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.46666666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>44</v>
       </c>
@@ -2673,39 +2531,17 @@
         <v>2</v>
       </c>
       <c r="D10" s="6">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6">
         <v>2</v>
       </c>
-      <c r="F10" s="6">
-        <v>2</v>
-      </c>
-      <c r="G10" s="6">
-        <v>21</v>
-      </c>
-      <c r="H10" s="11">
+      <c r="F10" s="8">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>36</v>
       </c>
@@ -2716,39 +2552,17 @@
         <v>5</v>
       </c>
       <c r="D11" s="6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E11" s="6">
-        <v>14</v>
-      </c>
-      <c r="F11" s="6">
         <v>5</v>
       </c>
-      <c r="G11" s="6">
-        <v>17</v>
-      </c>
-      <c r="H11" s="11">
+      <c r="F11" s="8">
         <f t="shared" si="0"/>
-        <v>2.7142857142857144</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.73684210526315785</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
@@ -2759,39 +2573,17 @@
         <v>2</v>
       </c>
       <c r="D12" s="6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E12" s="6">
-        <v>3</v>
-      </c>
-      <c r="F12" s="6">
-        <v>2</v>
-      </c>
-      <c r="G12" s="6">
-        <v>16</v>
-      </c>
-      <c r="H12" s="11">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="4"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
@@ -2802,39 +2594,17 @@
         <v>9</v>
       </c>
       <c r="D13" s="6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E13" s="6">
-        <v>6</v>
-      </c>
-      <c r="F13" s="6">
         <v>9</v>
       </c>
-      <c r="G13" s="6">
-        <v>17</v>
-      </c>
-      <c r="H13" s="11">
+      <c r="F13" s="8">
         <f t="shared" si="0"/>
-        <v>2.1428571428571428</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>47</v>
       </c>
@@ -2844,19 +2614,9 @@
       <c r="C14" s="6">
         <v>44</v>
       </c>
-      <c r="D14" s="6">
-        <v>170</v>
-      </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="I4:I13" formulaRange="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 

--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B0F9D27-3A12-462D-A569-EF3945346ED1}"/>
+  <xr:revisionPtr revIDLastSave="341" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71565E1A-B9F7-4D40-82F5-248252D4BA31}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="6" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="60">
   <si>
     <t>Maplewood HS</t>
   </si>
@@ -194,15 +194,42 @@
   <si>
     <t>Sum of Assists</t>
   </si>
+  <si>
+    <t>Sum of GBs</t>
+  </si>
+  <si>
+    <t>Sum of CTOs</t>
+  </si>
+  <si>
+    <t>Sum of TOs</t>
+  </si>
+  <si>
+    <t>Sum of WomanUpGoals</t>
+  </si>
+  <si>
+    <t>Sum of WomanDownGoals</t>
+  </si>
+  <si>
+    <t>Sum of Shots</t>
+  </si>
+  <si>
+    <t>Sum of ShotsFaced</t>
+  </si>
+  <si>
+    <t>Sum of Saves</t>
+  </si>
+  <si>
+    <t>Sum of DrawAtts</t>
+  </si>
+  <si>
+    <t>Sum of DrawControls</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,23 +247,8 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,14 +267,8 @@
         <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -285,21 +291,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -315,12 +311,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -494,7 +487,14 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="11"/>
     </cacheField>
     <cacheField name="Saves" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="8"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="8" count="6">
+        <n v="0"/>
+        <n v="4"/>
+        <n v="3"/>
+        <n v="8"/>
+        <n v="1"/>
+        <n v="5"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="WomanUpGoals" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
@@ -506,7 +506,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
     </cacheField>
     <cacheField name="PenType" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems containsBlank="1" count="5">
+        <m/>
+        <s v="Green"/>
+        <s v="Yellow"/>
+        <s v="12m"/>
+        <s v="Red"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="MinsServed" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
@@ -535,11 +541,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -555,11 +561,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -575,11 +581,11 @@
     <n v="4"/>
     <n v="3"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -595,11 +601,11 @@
     <n v="3"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -615,11 +621,11 @@
     <n v="2"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -635,11 +641,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -655,11 +661,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="3"/>
-    <s v="Green"/>
+    <x v="1"/>
     <n v="1"/>
   </r>
   <r>
@@ -675,11 +681,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -695,11 +701,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -715,11 +721,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -735,11 +741,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -755,11 +761,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -775,11 +781,11 @@
     <n v="4"/>
     <n v="3"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -795,11 +801,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -815,11 +821,11 @@
     <n v="4"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -835,11 +841,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -855,11 +861,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -875,11 +881,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <s v="Green"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="1"/>
     <n v="1"/>
   </r>
   <r>
@@ -895,11 +901,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="3"/>
-    <m/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -915,11 +921,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="8"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -935,11 +941,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v="Yellow"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="2"/>
     <n v="1"/>
   </r>
   <r>
@@ -955,11 +961,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -975,11 +981,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -995,11 +1001,11 @@
     <n v="1"/>
     <n v="1"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1015,11 +1021,11 @@
     <n v="3"/>
     <n v="3"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1035,11 +1041,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1055,11 +1061,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1075,11 +1081,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1095,11 +1101,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1115,11 +1121,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="9"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v="Green"/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
     <n v="1"/>
   </r>
   <r>
@@ -1135,11 +1141,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v="12m"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="3"/>
     <n v="0"/>
   </r>
   <r>
@@ -1155,11 +1161,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <s v="Yellow"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="2"/>
     <n v="1"/>
   </r>
   <r>
@@ -1175,11 +1181,11 @@
     <n v="4"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1195,11 +1201,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1215,11 +1221,11 @@
     <n v="3"/>
     <n v="1"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1235,11 +1241,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1255,11 +1261,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1275,11 +1281,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1295,11 +1301,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1315,11 +1321,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="8"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1335,11 +1341,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1355,11 +1361,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1375,11 +1381,11 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1395,11 +1401,11 @@
     <n v="4"/>
     <n v="3"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1415,11 +1421,11 @@
     <n v="1"/>
     <n v="1"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1435,11 +1441,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="3"/>
-    <m/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1455,11 +1461,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v="Green"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
     <n v="0"/>
   </r>
   <r>
@@ -1475,11 +1481,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="1"/>
     <n v="3"/>
-    <m/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1495,11 +1501,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1515,11 +1521,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="11"/>
-    <n v="8"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="3"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1535,11 +1541,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1555,11 +1561,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <s v="12m"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="3"/>
     <n v="0"/>
   </r>
   <r>
@@ -1575,11 +1581,11 @@
     <n v="2"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1595,11 +1601,11 @@
     <n v="4"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1615,11 +1621,11 @@
     <n v="3"/>
     <n v="1"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1635,11 +1641,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1655,11 +1661,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="3"/>
-    <s v="Yellow"/>
+    <x v="2"/>
     <n v="1"/>
   </r>
   <r>
@@ -1675,11 +1681,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="1"/>
     <n v="3"/>
-    <m/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1695,11 +1701,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1715,11 +1721,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v="12m"/>
+    <x v="4"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="3"/>
     <n v="0"/>
   </r>
   <r>
@@ -1735,11 +1741,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <s v="Yellow"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="2"/>
     <n v="1"/>
   </r>
   <r>
@@ -1755,11 +1761,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1775,11 +1781,11 @@
     <n v="2"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1795,11 +1801,11 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <s v="Red"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="4"/>
     <n v="0"/>
   </r>
   <r>
@@ -1815,11 +1821,11 @@
     <n v="1"/>
     <n v="1"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1835,11 +1841,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="1"/>
     <n v="3"/>
-    <m/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1855,11 +1861,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="0"/>
     <n v="3"/>
-    <m/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1875,11 +1881,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <m/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1895,11 +1901,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
     <n v="1"/>
     <n v="3"/>
-    <m/>
+    <x v="0"/>
     <n v="0"/>
   </r>
   <r>
@@ -1915,19 +1921,19 @@
     <n v="0"/>
     <n v="0"/>
     <n v="10"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <m/>
+    <x v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="0"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93B1F2E5-6101-4B7D-8463-217B5EDC7EF7}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93B1F2E5-6101-4B7D-8463-217B5EDC7EF7}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:M14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -1960,17 +1966,36 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -2014,17 +2039,57 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="12">
     <i>
       <x/>
     </i>
     <i i="1">
       <x v="1"/>
     </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+    <i i="6">
+      <x v="6"/>
+    </i>
+    <i i="7">
+      <x v="7"/>
+    </i>
+    <i i="8">
+      <x v="8"/>
+    </i>
+    <i i="9">
+      <x v="9"/>
+    </i>
+    <i i="10">
+      <x v="10"/>
+    </i>
+    <i i="11">
+      <x v="11"/>
+    </i>
   </colItems>
-  <dataFields count="2">
+  <dataFields count="12">
     <dataField name="Sum of Goals" fld="4" baseField="0" baseItem="0"/>
     <dataField name="Sum of Assists" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Sum of GBs" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Sum of TOs" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Sum of CTOs" fld="15" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Shots" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Sum of WomanUpGoals" fld="13" baseField="0" baseItem="0"/>
+    <dataField name="Sum of WomanDownGoals" fld="14" baseField="0" baseItem="0"/>
+    <dataField name="Sum of DrawAtts" fld="9" baseField="0" baseItem="0"/>
+    <dataField name="Sum of DrawControls" fld="10" baseField="0" baseItem="0"/>
+    <dataField name="Sum of ShotsFaced" fld="11" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Saves" fld="12" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -2355,29 +2420,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBA3C68-2291-42D7-93ED-B36167695E1B}">
-  <dimension ref="A3:F14"/>
+  <dimension ref="A3:M14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.26953125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6328125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
@@ -2387,14 +2448,38 @@
       <c r="C3" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>40</v>
       </c>
@@ -2405,17 +2490,37 @@
         <v>4</v>
       </c>
       <c r="D4" s="6">
+        <v>20</v>
+      </c>
+      <c r="E4" s="6">
         <v>6</v>
       </c>
-      <c r="E4" s="6">
-        <v>4</v>
-      </c>
-      <c r="F4" s="8">
-        <f>+D4/SUM(D4:E4)</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" s="6">
+        <v>9</v>
+      </c>
+      <c r="G4" s="6">
+        <v>17</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>17</v>
+      </c>
+      <c r="K4" s="6">
+        <v>11</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
@@ -2426,17 +2531,37 @@
         <v>3</v>
       </c>
       <c r="D5" s="6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E5" s="6">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6">
+        <v>11</v>
+      </c>
+      <c r="G5" s="6">
+        <v>11</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
         <v>3</v>
       </c>
-      <c r="F5" s="8">
-        <f t="shared" ref="F5:F13" si="0">+D5/SUM(D5:E5)</f>
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>38</v>
       </c>
@@ -2447,17 +2572,37 @@
         <v>8</v>
       </c>
       <c r="D6" s="6">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6">
+        <v>5</v>
+      </c>
+      <c r="F6" s="6">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6">
+        <v>16</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <v>17</v>
+      </c>
+      <c r="K6" s="6">
         <v>8</v>
       </c>
-      <c r="E6" s="6">
-        <v>8</v>
-      </c>
-      <c r="F6" s="8">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
@@ -2468,17 +2613,37 @@
         <v>3</v>
       </c>
       <c r="D7" s="6">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E7" s="6">
+        <v>8</v>
+      </c>
+      <c r="F7" s="6">
+        <v>11</v>
+      </c>
+      <c r="G7" s="6">
+        <v>13</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
         <v>3</v>
       </c>
-      <c r="F7" s="8">
-        <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>45</v>
       </c>
@@ -2489,17 +2654,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>56</v>
+      </c>
+      <c r="M8" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
@@ -2510,17 +2695,37 @@
         <v>8</v>
       </c>
       <c r="D9" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6">
-        <v>8</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" si="0"/>
-        <v>0.46666666666666667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6">
+        <v>4</v>
+      </c>
+      <c r="G9" s="6">
+        <v>21</v>
+      </c>
+      <c r="H9" s="6">
+        <v>2</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>44</v>
       </c>
@@ -2531,17 +2736,37 @@
         <v>2</v>
       </c>
       <c r="D10" s="6">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E10" s="6">
-        <v>2</v>
-      </c>
-      <c r="F10" s="8">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6">
+        <v>11</v>
+      </c>
+      <c r="G10" s="6">
+        <v>9</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>4</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>36</v>
       </c>
@@ -2552,17 +2777,37 @@
         <v>5</v>
       </c>
       <c r="D11" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="6">
-        <v>5</v>
-      </c>
-      <c r="F11" s="8">
-        <f t="shared" si="0"/>
-        <v>0.73684210526315785</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="F11" s="6">
+        <v>3</v>
+      </c>
+      <c r="G11" s="6">
+        <v>26</v>
+      </c>
+      <c r="H11" s="6">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
@@ -2573,17 +2818,37 @@
         <v>2</v>
       </c>
       <c r="D12" s="6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E12" s="6">
-        <v>2</v>
-      </c>
-      <c r="F12" s="8">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="F12" s="6">
+        <v>13</v>
+      </c>
+      <c r="G12" s="6">
+        <v>7</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>2</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
@@ -2594,17 +2859,37 @@
         <v>9</v>
       </c>
       <c r="D13" s="6">
+        <v>17</v>
+      </c>
+      <c r="E13" s="6">
+        <v>12</v>
+      </c>
+      <c r="F13" s="6">
         <v>6</v>
       </c>
-      <c r="E13" s="6">
-        <v>9</v>
-      </c>
-      <c r="F13" s="8">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="6">
+        <v>14</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>13</v>
+      </c>
+      <c r="K13" s="6">
+        <v>6</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>47</v>
       </c>
@@ -2613,6 +2898,36 @@
       </c>
       <c r="C14" s="6">
         <v>44</v>
+      </c>
+      <c r="D14" s="6">
+        <v>170</v>
+      </c>
+      <c r="E14" s="6">
+        <v>79</v>
+      </c>
+      <c r="F14" s="6">
+        <v>72</v>
+      </c>
+      <c r="G14" s="6">
+        <v>134</v>
+      </c>
+      <c r="H14" s="6">
+        <v>5</v>
+      </c>
+      <c r="I14" s="6">
+        <v>12</v>
+      </c>
+      <c r="J14" s="6">
+        <v>47</v>
+      </c>
+      <c r="K14" s="6">
+        <v>25</v>
+      </c>
+      <c r="L14" s="6">
+        <v>56</v>
+      </c>
+      <c r="M14" s="6">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -8,21 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="341" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71565E1A-B9F7-4D40-82F5-248252D4BA31}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99650D74-B084-410F-ACA1-B56DBBEA8042}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
-    <sheet name="FactTable" sheetId="2" r:id="rId2"/>
+    <sheet name="FactTable" sheetId="2" r:id="rId1"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId2"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId4"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="46">
   <si>
     <t>Maplewood HS</t>
   </si>
@@ -182,48 +178,6 @@
   <si>
     <t>Lauren Scott</t>
   </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Sum of Goals</t>
-  </si>
-  <si>
-    <t>Sum of Assists</t>
-  </si>
-  <si>
-    <t>Sum of GBs</t>
-  </si>
-  <si>
-    <t>Sum of CTOs</t>
-  </si>
-  <si>
-    <t>Sum of TOs</t>
-  </si>
-  <si>
-    <t>Sum of WomanUpGoals</t>
-  </si>
-  <si>
-    <t>Sum of WomanDownGoals</t>
-  </si>
-  <si>
-    <t>Sum of Shots</t>
-  </si>
-  <si>
-    <t>Sum of ShotsFaced</t>
-  </si>
-  <si>
-    <t>Sum of Saves</t>
-  </si>
-  <si>
-    <t>Sum of DrawAtts</t>
-  </si>
-  <si>
-    <t>Sum of DrawControls</t>
-  </si>
 </sst>
 </file>
 
@@ -295,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -306,11 +260,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,1684 +372,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Chris Napoli" refreshedDate="46084.654355555555" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="70" xr:uid="{45BECAE6-F96A-464F-B8E1-6CE7A28CF657}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:R71" sheet="FactTable"/>
-  </cacheSource>
-  <cacheFields count="18">
-    <cacheField name="PlayerID" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
-    </cacheField>
-    <cacheField name="F_PlayerName" numFmtId="0">
-      <sharedItems count="10">
-        <s v="Olivia Hart"/>
-        <s v="Mia Russo"/>
-        <s v="Emma Torres"/>
-        <s v="Sophie Kim"/>
-        <s v="Ava Nguyen"/>
-        <s v="Chloe Banks"/>
-        <s v="Riley Patel"/>
-        <s v="Jenna Walsh"/>
-        <s v="Natalie Cruz"/>
-        <s v="Lauren Scott"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Date" numFmtId="0">
-      <sharedItems count="7">
-        <s v="2025-03-08"/>
-        <s v="2025-03-15"/>
-        <s v="2025-03-22"/>
-        <s v="2025-03-29"/>
-        <s v="2025-04-05"/>
-        <s v="2025-04-12"/>
-        <s v="2025-04-19"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="OpponentName" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Goals" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="Assists" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="2"/>
-    </cacheField>
-    <cacheField name="Shots" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="7"/>
-    </cacheField>
-    <cacheField name="GBs" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="5"/>
-    </cacheField>
-    <cacheField name="TOs" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="DrawAtts" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="4"/>
-    </cacheField>
-    <cacheField name="DrawControls" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="ShotsFaced" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="11"/>
-    </cacheField>
-    <cacheField name="Saves" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="8" count="6">
-        <n v="0"/>
-        <n v="4"/>
-        <n v="3"/>
-        <n v="8"/>
-        <n v="1"/>
-        <n v="5"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="WomanUpGoals" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="WomanDownGoals" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="CTOs" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="PenType" numFmtId="0">
-      <sharedItems containsBlank="1" count="5">
-        <m/>
-        <s v="Green"/>
-        <s v="Yellow"/>
-        <s v="12m"/>
-        <s v="Red"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="MinsServed" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="70">
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="1"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <x v="0"/>
-    <s v="Riverside HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="5"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <x v="1"/>
-    <s v="Lakewood HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="8"/>
-    <x v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="2"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <x v="2"/>
-    <s v="Northview HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="9"/>
-    <x v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="7"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <x v="3"/>
-    <s v="Summit Academy"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="8"/>
-    <x v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="1"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <x v="4"/>
-    <s v="Eastbrook HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="11"/>
-    <x v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="2"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="5"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <x v="5"/>
-    <s v="Cedar Falls HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="5"/>
-    <x v="4"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="6"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="4"/>
-    <x v="3"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="4"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="5"/>
-    <x v="4"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="6"/>
-    <x v="5"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="6"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="8"/>
-    <x v="7"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="9"/>
-    <x v="8"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="3"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <n v="10"/>
-    <x v="9"/>
-    <x v="6"/>
-    <s v="Maplewood HS"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="10"/>
-    <x v="5"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="0"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{93B1F2E5-6101-4B7D-8463-217B5EDC7EF7}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:M14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
-    <i i="6">
-      <x v="6"/>
-    </i>
-    <i i="7">
-      <x v="7"/>
-    </i>
-    <i i="8">
-      <x v="8"/>
-    </i>
-    <i i="9">
-      <x v="9"/>
-    </i>
-    <i i="10">
-      <x v="10"/>
-    </i>
-    <i i="11">
-      <x v="11"/>
-    </i>
-  </colItems>
-  <dataFields count="12">
-    <dataField name="Sum of Goals" fld="4" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Assists" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Sum of GBs" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Sum of TOs" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Sum of CTOs" fld="15" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Shots" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Sum of WomanUpGoals" fld="13" baseField="0" baseItem="0"/>
-    <dataField name="Sum of WomanDownGoals" fld="14" baseField="0" baseItem="0"/>
-    <dataField name="Sum of DrawAtts" fld="9" baseField="0" baseItem="0"/>
-    <dataField name="Sum of DrawControls" fld="10" baseField="0" baseItem="0"/>
-    <dataField name="Sum of ShotsFaced" fld="11" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Saves" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2419,523 +690,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBA3C68-2291-42D7-93ED-B36167695E1B}">
-  <dimension ref="A3:M14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="6">
-        <v>6</v>
-      </c>
-      <c r="C4" s="6">
-        <v>4</v>
-      </c>
-      <c r="D4" s="6">
-        <v>20</v>
-      </c>
-      <c r="E4" s="6">
-        <v>6</v>
-      </c>
-      <c r="F4" s="6">
-        <v>9</v>
-      </c>
-      <c r="G4" s="6">
-        <v>17</v>
-      </c>
-      <c r="H4" s="6">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>17</v>
-      </c>
-      <c r="K4" s="6">
-        <v>11</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="6">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6">
-        <v>3</v>
-      </c>
-      <c r="D5" s="6">
-        <v>21</v>
-      </c>
-      <c r="E5" s="6">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6">
-        <v>11</v>
-      </c>
-      <c r="G5" s="6">
-        <v>11</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <v>3</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="6">
-        <v>8</v>
-      </c>
-      <c r="C6" s="6">
-        <v>8</v>
-      </c>
-      <c r="D6" s="6">
-        <v>18</v>
-      </c>
-      <c r="E6" s="6">
-        <v>5</v>
-      </c>
-      <c r="F6" s="6">
-        <v>4</v>
-      </c>
-      <c r="G6" s="6">
-        <v>16</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>17</v>
-      </c>
-      <c r="K6" s="6">
-        <v>8</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="6">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6">
-        <v>24</v>
-      </c>
-      <c r="E7" s="6">
-        <v>8</v>
-      </c>
-      <c r="F7" s="6">
-        <v>11</v>
-      </c>
-      <c r="G7" s="6">
-        <v>13</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>3</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>6</v>
-      </c>
-      <c r="E8" s="6">
-        <v>6</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>56</v>
-      </c>
-      <c r="M8" s="6">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="6">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6">
-        <v>8</v>
-      </c>
-      <c r="D9" s="6">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6">
-        <v>9</v>
-      </c>
-      <c r="F9" s="6">
-        <v>4</v>
-      </c>
-      <c r="G9" s="6">
-        <v>21</v>
-      </c>
-      <c r="H9" s="6">
-        <v>2</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="6">
-        <v>2</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="6">
-        <v>21</v>
-      </c>
-      <c r="E10" s="6">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6">
-        <v>11</v>
-      </c>
-      <c r="G10" s="6">
-        <v>9</v>
-      </c>
-      <c r="H10" s="6">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6">
-        <v>4</v>
-      </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="6">
-        <v>14</v>
-      </c>
-      <c r="C11" s="6">
-        <v>5</v>
-      </c>
-      <c r="D11" s="6">
-        <v>17</v>
-      </c>
-      <c r="E11" s="6">
-        <v>4</v>
-      </c>
-      <c r="F11" s="6">
-        <v>3</v>
-      </c>
-      <c r="G11" s="6">
-        <v>26</v>
-      </c>
-      <c r="H11" s="6">
-        <v>2</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="6">
-        <v>3</v>
-      </c>
-      <c r="C12" s="6">
-        <v>2</v>
-      </c>
-      <c r="D12" s="6">
-        <v>16</v>
-      </c>
-      <c r="E12" s="6">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6">
-        <v>13</v>
-      </c>
-      <c r="G12" s="6">
-        <v>7</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6">
-        <v>2</v>
-      </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="6">
-        <v>6</v>
-      </c>
-      <c r="C13" s="6">
-        <v>9</v>
-      </c>
-      <c r="D13" s="6">
-        <v>17</v>
-      </c>
-      <c r="E13" s="6">
-        <v>12</v>
-      </c>
-      <c r="F13" s="6">
-        <v>6</v>
-      </c>
-      <c r="G13" s="6">
-        <v>14</v>
-      </c>
-      <c r="H13" s="6">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6">
-        <v>13</v>
-      </c>
-      <c r="K13" s="6">
-        <v>6</v>
-      </c>
-      <c r="L13" s="6">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="6">
-        <v>57</v>
-      </c>
-      <c r="C14" s="6">
-        <v>44</v>
-      </c>
-      <c r="D14" s="6">
-        <v>170</v>
-      </c>
-      <c r="E14" s="6">
-        <v>79</v>
-      </c>
-      <c r="F14" s="6">
-        <v>72</v>
-      </c>
-      <c r="G14" s="6">
-        <v>134</v>
-      </c>
-      <c r="H14" s="6">
-        <v>5</v>
-      </c>
-      <c r="I14" s="6">
-        <v>12</v>
-      </c>
-      <c r="J14" s="6">
-        <v>47</v>
-      </c>
-      <c r="K14" s="6">
-        <v>25</v>
-      </c>
-      <c r="L14" s="6">
-        <v>56</v>
-      </c>
-      <c r="M14" s="6">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{675130FE-5529-48C3-883E-D019D34D4137}">
   <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="342" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99650D74-B084-410F-ACA1-B56DBBEA8042}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{511952F7-274B-4F44-A6D1-4DD9ACB4E69A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
@@ -374,6 +374,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="343" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{511952F7-274B-4F44-A6D1-4DD9ACB4E69A}"/>
+  <xr:revisionPtr revIDLastSave="351" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{295C1F71-4C65-431C-8576-6E62310EB1F0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
+    <workbookView xWindow="28680" yWindow="-7935" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
   <sheets>
     <sheet name="FactTable" sheetId="2" r:id="rId1"/>

--- a/Test_Data/FactTable.xlsx
+++ b/Test_Data/FactTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="351" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{295C1F71-4C65-431C-8576-6E62310EB1F0}"/>
+  <xr:revisionPtr revIDLastSave="352" documentId="8_{6D691F99-DFB6-41F9-ABE0-713B804467D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAEE05FA-3900-47AA-9477-21A36F027E6B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-7935" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
+    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{FADB34D3-2AD0-4900-91AC-1DDA22919594}"/>
   </bookViews>
   <sheets>
     <sheet name="FactTable" sheetId="2" r:id="rId1"/>
@@ -4644,5 +4644,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>